--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260918.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>14,632,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,129,073</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,632,000</t>
+          <t>16,129,073</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
